--- a/Ficheiros EXCEL/AUC/Distribuicao_teste22082026_20260823_0128.xlsx
+++ b/Ficheiros EXCEL/AUC/Distribuicao_teste22082026_20260823_0128.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="11_C0CC78E4AD7B479EB0619AC95693A9673DACB912" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="525" yWindow="-15810" windowWidth="27390" windowHeight="15165" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="525" yWindow="-15810" windowWidth="27390" windowHeight="15165" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Armazéns" sheetId="1" r:id="rId1"/>
